--- a/output/pdf_financials_xlsx/IZZ.xlsx
+++ b/output/pdf_financials_xlsx/IZZ.xlsx
@@ -1201,13 +1201,13 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.276605</v>
+        <v>-0.276605</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.08885999999999999</v>
+        <v>-0.08885999999999999</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.491477</v>
+        <v>-0.491477</v>
       </c>
       <c r="E16" s="1" t="inlineStr">
         <is>
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.276605</v>
+        <v>-0.276605</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.08885999999999999</v>
+        <v>-0.08885999999999999</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.491477</v>
+        <v>-0.491477</v>
       </c>
       <c r="E20" s="1" t="inlineStr">
         <is>
@@ -1605,13 +1605,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.276605</v>
+        <v>-0.276605</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.08885999999999999</v>
+        <v>-0.08885999999999999</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.491477</v>
+        <v>-0.491477</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>-0.194789</v>
@@ -1831,13 +1831,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.276605</v>
+        <v>-0.276605</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.08885999999999999</v>
+        <v>-0.08885999999999999</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.491477</v>
+        <v>-0.491477</v>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
@@ -1943,13 +1943,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.276605</v>
+        <v>-0.276605</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.08885999999999999</v>
+        <v>-0.08885999999999999</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.491477</v>
+        <v>-0.491477</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -2061,13 +2061,13 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="1" t="inlineStr">
         <is>
@@ -22430,13 +22430,13 @@
         </is>
       </c>
       <c r="E235" s="5" t="n">
-        <v>0.276605</v>
+        <v>-0.276605</v>
       </c>
       <c r="F235" s="5" t="n">
-        <v>0.08885999999999999</v>
+        <v>-0.08885999999999999</v>
       </c>
       <c r="G235" s="5" t="n">
-        <v>0.491477</v>
+        <v>-0.491477</v>
       </c>
       <c r="H235" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/IZZ.xlsx
+++ b/output/pdf_financials_xlsx/IZZ.xlsx
@@ -977,10 +977,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000837</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00013</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.276605</v>
+        <v>-0.275768</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.08885999999999999</v>
+        <v>-0.08873</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.491477</v>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.276605</v>
+        <v>-0.275768</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.08885999999999999</v>
+        <v>-0.08873</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.491477</v>
@@ -2207,7 +2207,7 @@
         <v>0.445345</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0.409808</v>
+        <v>0.445345</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>0.041785</v>
@@ -2287,7 +2287,7 @@
         <v>0.445345</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.409808</v>
+        <v>0.445345</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>0.341785</v>
@@ -2767,7 +2767,7 @@
         <v>0.059497</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.09705999999999999</v>
+        <v>0.061523</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>0.013948</v>
@@ -9044,7 +9044,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -22069,7 +22069,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E230" s="5" t="n">
@@ -22142,7 +22142,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E231" s="5" t="n">

--- a/output/pdf_financials_xlsx/IZZ.xlsx
+++ b/output/pdf_financials_xlsx/IZZ.xlsx
@@ -16621,7 +16621,11 @@
           <t>Proceeds from private placement 10</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
@@ -17530,7 +17534,11 @@
           <t>Proceeds from issuance of units under a private placement 10</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E165" t="inlineStr">
         <is>
           <t>-</t>
@@ -18001,7 +18009,11 @@
           <t>Proceeds from issuance of units under a private placement</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
           <t>-</t>
@@ -18764,7 +18776,11 @@
           <t>Issuance of units under a private placement 10</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E183" t="inlineStr">
         <is>
           <t>-</t>
